--- a/public/template/Pemindahbukuan  gaji PNS Mei.xlsx
+++ b/public/template/Pemindahbukuan  gaji PNS Mei.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\spp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\var\www\jadwal\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AEB7D8-19EB-4971-A316-52DC28D593FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131F4630-2D2E-424A-AB78-1C32DFAF84E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PENGANTAR" sheetId="1" r:id="rId1"/>
     <sheet name="DATA PRINT" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">PENGANTAR!$A$1:$K$51</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -95,9 +101,6 @@
   </si>
   <si>
     <t>GAJI BRUTO</t>
-  </si>
-  <si>
-    <t>POT LAINYA</t>
   </si>
   <si>
     <t>GAJI BERSIH</t>
@@ -289,9 +292,6 @@
     <t xml:space="preserve">     Sehubungan dengan pembayaran gaji ASN bulan Mei 2025 bersama ini kami mohon</t>
   </si>
   <si>
-    <t xml:space="preserve">  Plt. Camat Watumalang</t>
-  </si>
-  <si>
     <t>Plt. Camat Watumalang</t>
   </si>
   <si>
@@ -299,6 +299,12 @@
   </si>
   <si>
     <t>NIP. 19680331 199603 1 007</t>
+  </si>
+  <si>
+    <t>Camat Watumalang</t>
+  </si>
+  <si>
+    <t>POT. LAINYA</t>
   </si>
 </sst>
 </file>
@@ -312,7 +318,7 @@
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="&quot;Rp&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -502,6 +508,19 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -942,9 +961,139 @@
     <xf numFmtId="168" fontId="27" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="5" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="8"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="17" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="18" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -966,142 +1115,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="8"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="17" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="18" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1143,6 +1156,12 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -1174,15 +1193,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>127001</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>95546</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>641350</xdr:colOff>
+      <xdr:colOff>569143</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:rowOff>60738</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1212,8 +1231,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="990600" cy="1060450"/>
+          <a:off x="127001" y="95546"/>
+          <a:ext cx="790012" cy="843149"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1618,151 +1637,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" customFormat="1" ht="17.5">
-      <c r="A1" s="93" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
+      <c r="A1" s="118" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
       <c r="L1" s="17"/>
       <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" customFormat="1" ht="23">
-      <c r="A2" s="94" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
+      <c r="A2" s="117" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
       <c r="L2" s="18"/>
       <c r="M2" s="18"/>
     </row>
     <row r="3" spans="1:13" customFormat="1">
-      <c r="A3" s="68" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+      <c r="A3" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
       <c r="L3" s="19"/>
       <c r="M3" s="19"/>
     </row>
     <row r="4" spans="1:13" customFormat="1">
-      <c r="A4" s="68" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
+      <c r="A4" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
       <c r="L4" s="19"/>
       <c r="M4" s="19"/>
     </row>
     <row r="5" spans="1:13" customFormat="1">
-      <c r="A5" s="68" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
+      <c r="A5" s="60" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
       <c r="L5" s="19"/>
       <c r="M5" s="19"/>
     </row>
     <row r="6" spans="1:13" customFormat="1" ht="15" thickBot="1">
-      <c r="A6" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
+      <c r="A6" s="93" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="93"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
       <c r="L6" s="19"/>
       <c r="M6" s="19"/>
     </row>
     <row r="7" spans="1:13" ht="3.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="79"/>
-      <c r="B7" s="79"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79"/>
+      <c r="A7" s="72"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="72"/>
     </row>
     <row r="8" spans="1:13" ht="3" customHeight="1">
-      <c r="A8" s="80"/>
-      <c r="B8" s="80"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80"/>
+      <c r="A8" s="73"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="73"/>
     </row>
     <row r="9" spans="1:13" ht="15.5">
       <c r="G9" s="29"/>
-      <c r="H9" s="96" t="s">
-        <v>78</v>
-      </c>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
+      <c r="H9" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9" s="68"/>
+      <c r="J9" s="68"/>
+      <c r="K9" s="68"/>
     </row>
     <row r="11" spans="1:13" ht="15.5">
-      <c r="A11" s="81" t="s">
+      <c r="A11" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="81"/>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
@@ -1770,14 +1789,14 @@
       <c r="K11" s="13"/>
     </row>
     <row r="12" spans="1:13" ht="15.5">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="81"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
@@ -1785,14 +1804,14 @@
       <c r="K12" s="13"/>
     </row>
     <row r="13" spans="1:13" ht="15.5">
-      <c r="A13" s="81" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="81"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
+      <c r="A13" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="74"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
@@ -1807,14 +1826,14 @@
       <c r="K14" s="13"/>
     </row>
     <row r="15" spans="1:13" ht="15.5">
-      <c r="A15" s="70" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="70"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
+      <c r="A15" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="76"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="76"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
@@ -1822,14 +1841,14 @@
       <c r="K15" s="12"/>
     </row>
     <row r="16" spans="1:13" ht="15.5">
-      <c r="A16" s="70" t="s">
+      <c r="A16" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="70"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="76"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="76"/>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
@@ -1837,14 +1856,14 @@
       <c r="K16" s="12"/>
     </row>
     <row r="17" spans="1:15" ht="15.5">
-      <c r="A17" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="70"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
+      <c r="A17" s="76" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="76"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="76"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
@@ -1853,11 +1872,11 @@
     </row>
     <row r="18" spans="1:15" ht="15.5">
       <c r="A18" s="14"/>
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
       <c r="G18" s="13"/>
@@ -1874,13 +1893,13 @@
       <c r="K19" s="14"/>
     </row>
     <row r="21" spans="1:15" ht="15.5">
-      <c r="A21" s="82" t="s">
+      <c r="A21" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -1902,19 +1921,19 @@
       <c r="K22" s="2"/>
     </row>
     <row r="23" spans="1:15" ht="15.5">
-      <c r="A23" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="57"/>
+      <c r="A23" s="101" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="101"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="101"/>
+      <c r="G23" s="101"/>
+      <c r="H23" s="101"/>
+      <c r="I23" s="101"/>
+      <c r="J23" s="101"/>
+      <c r="K23" s="101"/>
       <c r="L23" s="3"/>
     </row>
     <row r="24" spans="1:15" ht="15.5">
@@ -1934,28 +1953,28 @@
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="1:15" ht="15.5">
-      <c r="A25" s="58"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
+      <c r="A25" s="102"/>
+      <c r="B25" s="102"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="102"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="102"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="102"/>
+      <c r="K25" s="102"/>
     </row>
     <row r="26" spans="1:15" ht="15.5">
       <c r="A26" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="29" t="s">
         <v>75</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>76</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
@@ -1967,11 +1986,11 @@
     </row>
     <row r="27" spans="1:15" ht="15.5">
       <c r="A27" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D27" s="50">
         <f>J34</f>
@@ -1986,79 +2005,79 @@
       <c r="K27" s="4"/>
     </row>
     <row r="28" spans="1:15" ht="15.5">
-      <c r="A28" s="83" t="s">
+      <c r="A28" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="83"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="77"/>
+      <c r="K28" s="77"/>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1">
-      <c r="A29" s="65" t="s">
+      <c r="A29" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="84" t="s">
+      <c r="B29" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="85"/>
-      <c r="D29" s="85"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="65" t="s">
+      <c r="C29" s="80"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65" t="s">
+      <c r="G29" s="78"/>
+      <c r="H29" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65" t="s">
+      <c r="I29" s="78"/>
+      <c r="J29" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="K29" s="65"/>
+      <c r="K29" s="78"/>
     </row>
     <row r="30" spans="1:15" ht="12.75" customHeight="1">
-      <c r="A30" s="65"/>
-      <c r="B30" s="87"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="88"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="66"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="65"/>
+      <c r="A30" s="78"/>
+      <c r="B30" s="82"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="78"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="92"/>
+      <c r="I30" s="92"/>
+      <c r="J30" s="78"/>
+      <c r="K30" s="78"/>
     </row>
     <row r="31" spans="1:15" ht="15.5">
       <c r="A31" s="5">
         <v>1</v>
       </c>
-      <c r="B31" s="59" t="s">
+      <c r="B31" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="63" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31" s="64"/>
-      <c r="H31" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="I31" s="54"/>
-      <c r="J31" s="51">
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31" s="91"/>
+      <c r="H31" s="97" t="s">
+        <v>64</v>
+      </c>
+      <c r="I31" s="98"/>
+      <c r="J31" s="67">
         <f>'DATA PRINT'!G21</f>
         <v>60066737.5</v>
       </c>
-      <c r="K31" s="52"/>
+      <c r="K31" s="96"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
       <c r="O31" s="7"/>
@@ -2067,25 +2086,25 @@
       <c r="A32" s="5">
         <v>2</v>
       </c>
-      <c r="B32" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="63" t="s">
-        <v>63</v>
-      </c>
-      <c r="G32" s="67"/>
-      <c r="H32" s="90" t="s">
-        <v>23</v>
-      </c>
-      <c r="I32" s="91"/>
-      <c r="J32" s="95">
+      <c r="B32" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="64" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32" s="65"/>
+      <c r="H32" s="85" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="86"/>
+      <c r="J32" s="66">
         <f>'DATA PRINT'!E21</f>
         <v>1543762.5</v>
       </c>
-      <c r="K32" s="51"/>
+      <c r="K32" s="67"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
       <c r="O32" s="7"/>
@@ -2094,76 +2113,76 @@
       <c r="A33" s="5">
         <v>3</v>
       </c>
-      <c r="B33" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" s="60"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="63" t="s">
-        <v>64</v>
-      </c>
-      <c r="G33" s="67"/>
-      <c r="H33" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="I33" s="56"/>
-      <c r="J33" s="95">
+      <c r="B33" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="62"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="G33" s="65"/>
+      <c r="H33" s="99" t="s">
+        <v>65</v>
+      </c>
+      <c r="I33" s="100"/>
+      <c r="J33" s="66">
         <f>'DATA PRINT'!F21</f>
         <v>140000</v>
       </c>
-      <c r="K33" s="51"/>
+      <c r="K33" s="67"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
       <c r="O33" s="7"/>
     </row>
     <row r="34" spans="1:15" ht="18.75" customHeight="1">
-      <c r="A34" s="65" t="s">
+      <c r="A34" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="65"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="65"/>
-      <c r="H34" s="74"/>
-      <c r="I34" s="74"/>
-      <c r="J34" s="72">
+      <c r="B34" s="78"/>
+      <c r="C34" s="78"/>
+      <c r="D34" s="78"/>
+      <c r="E34" s="78"/>
+      <c r="F34" s="78"/>
+      <c r="G34" s="78"/>
+      <c r="H34" s="87"/>
+      <c r="I34" s="87"/>
+      <c r="J34" s="95">
         <f>SUM(J31:K33)</f>
         <v>61750500</v>
       </c>
-      <c r="K34" s="72"/>
+      <c r="K34" s="95"/>
       <c r="M34" s="8"/>
       <c r="N34" s="6"/>
       <c r="O34" s="7"/>
     </row>
     <row r="35" spans="1:15" ht="5.25" customHeight="1">
       <c r="A35" s="9"/>
-      <c r="B35" s="62"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="62"/>
-      <c r="J35" s="62"/>
-      <c r="K35" s="62"/>
+      <c r="B35" s="54"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
       <c r="L35" s="10"/>
     </row>
     <row r="36" spans="1:15" ht="3" customHeight="1">
-      <c r="A36" s="76"/>
-      <c r="B36" s="76"/>
-      <c r="C36" s="76"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="92"/>
-      <c r="K36" s="92"/>
+      <c r="A36" s="89"/>
+      <c r="B36" s="89"/>
+      <c r="C36" s="89"/>
+      <c r="D36" s="89"/>
+      <c r="E36" s="89"/>
+      <c r="F36" s="89"/>
+      <c r="G36" s="89"/>
+      <c r="H36" s="88"/>
+      <c r="I36" s="88"/>
+      <c r="J36" s="90"/>
+      <c r="K36" s="90"/>
       <c r="L36" s="10"/>
       <c r="O36" s="6"/>
     </row>
@@ -2177,7 +2196,7 @@
     </row>
     <row r="38" spans="1:15" ht="15.5">
       <c r="A38" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -2193,19 +2212,19 @@
       <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15" ht="15.5">
-      <c r="A39" s="81" t="s">
+      <c r="A39" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="B39" s="81"/>
-      <c r="C39" s="81"/>
-      <c r="D39" s="81"/>
-      <c r="E39" s="81"/>
-      <c r="F39" s="81"/>
-      <c r="G39" s="81"/>
-      <c r="H39" s="81"/>
-      <c r="I39" s="81"/>
-      <c r="J39" s="81"/>
-      <c r="K39" s="81"/>
+      <c r="B39" s="74"/>
+      <c r="C39" s="74"/>
+      <c r="D39" s="74"/>
+      <c r="E39" s="74"/>
+      <c r="F39" s="74"/>
+      <c r="G39" s="74"/>
+      <c r="H39" s="74"/>
+      <c r="I39" s="74"/>
+      <c r="J39" s="74"/>
+      <c r="K39" s="74"/>
       <c r="O39" s="6"/>
     </row>
     <row r="40" spans="1:15" ht="15.5">
@@ -2224,19 +2243,19 @@
       <c r="O40" s="11"/>
     </row>
     <row r="41" spans="1:15" ht="15.5">
-      <c r="A41" s="78" t="s">
+      <c r="A41" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="78"/>
-      <c r="C41" s="78"/>
-      <c r="D41" s="78"/>
-      <c r="E41" s="78"/>
-      <c r="F41" s="78"/>
-      <c r="G41" s="78"/>
-      <c r="H41" s="78"/>
-      <c r="I41" s="78"/>
-      <c r="J41" s="78"/>
-      <c r="K41" s="78"/>
+      <c r="B41" s="71"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="71"/>
+      <c r="K41" s="71"/>
       <c r="N41" s="11"/>
       <c r="O41" s="11"/>
     </row>
@@ -2255,58 +2274,58 @@
       <c r="O42" s="6"/>
     </row>
     <row r="43" spans="1:15" ht="15.5">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="73"/>
-      <c r="C43" s="73"/>
-      <c r="D43" s="73"/>
-      <c r="E43" s="73"/>
+      <c r="B43" s="70"/>
+      <c r="C43" s="70"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="73"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="73"/>
-      <c r="K43" s="73"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="70"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="70"/>
     </row>
     <row r="44" spans="1:15" ht="15.5">
-      <c r="A44" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="73"/>
-      <c r="C44" s="73"/>
-      <c r="D44" s="73"/>
-      <c r="E44" s="73"/>
+      <c r="A44" s="70" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="70"/>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="73" t="s">
-        <v>24</v>
-      </c>
-      <c r="I44" s="73"/>
-      <c r="J44" s="73"/>
-      <c r="K44" s="73"/>
+      <c r="H44" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="70"/>
+      <c r="J44" s="70"/>
+      <c r="K44" s="70"/>
     </row>
     <row r="45" spans="1:15" ht="15.5">
-      <c r="A45" s="73" t="s">
+      <c r="A45" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="73"/>
-      <c r="C45" s="73"/>
-      <c r="D45" s="73"/>
-      <c r="E45" s="73"/>
+      <c r="B45" s="70"/>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="73"/>
-      <c r="I45" s="73"/>
-      <c r="J45" s="73"/>
-      <c r="K45" s="73"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="70"/>
+      <c r="K45" s="70"/>
     </row>
     <row r="46" spans="1:15" ht="15.5">
-      <c r="A46" s="77"/>
-      <c r="B46" s="77"/>
-      <c r="C46" s="77"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="77"/>
+      <c r="A46" s="69"/>
+      <c r="B46" s="69"/>
+      <c r="C46" s="69"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -2328,52 +2347,52 @@
       <c r="K47" s="2"/>
     </row>
     <row r="48" spans="1:15" ht="15.5">
-      <c r="A48" s="100"/>
-      <c r="B48" s="100"/>
-      <c r="C48" s="100"/>
-      <c r="D48" s="100"/>
-      <c r="E48" s="100"/>
+      <c r="A48" s="55"/>
+      <c r="B48" s="55"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="55"/>
+      <c r="E48" s="55"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="100"/>
-      <c r="I48" s="100"/>
-      <c r="J48" s="100"/>
-      <c r="K48" s="100"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="55"/>
+      <c r="J48" s="55"/>
+      <c r="K48" s="55"/>
     </row>
     <row r="49" spans="1:12" ht="15.5">
-      <c r="A49" s="99" t="s">
-        <v>83</v>
-      </c>
-      <c r="B49" s="99"/>
-      <c r="C49" s="99"/>
-      <c r="D49" s="99"/>
-      <c r="E49" s="99"/>
+      <c r="A49" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="53"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="53"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="98" t="s">
-        <v>43</v>
-      </c>
-      <c r="I49" s="98"/>
-      <c r="J49" s="98"/>
-      <c r="K49" s="98"/>
+      <c r="H49" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="I49" s="52"/>
+      <c r="J49" s="52"/>
+      <c r="K49" s="52"/>
       <c r="L49" s="13"/>
     </row>
     <row r="50" spans="1:12" ht="15.5">
-      <c r="A50" s="101" t="s">
-        <v>84</v>
-      </c>
-      <c r="B50" s="101"/>
-      <c r="C50" s="101"/>
-      <c r="D50" s="101"/>
-      <c r="E50" s="101"/>
+      <c r="A50" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="56"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="56"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="102" t="s">
-        <v>67</v>
-      </c>
-      <c r="I50" s="102"/>
-      <c r="J50" s="102"/>
-      <c r="K50" s="102"/>
+      <c r="H50" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="I50" s="57"/>
+      <c r="J50" s="57"/>
+      <c r="K50" s="57"/>
     </row>
     <row r="51" spans="1:12" ht="18">
       <c r="A51" s="16"/>
@@ -2388,8 +2407,8 @@
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
       <c r="D52"/>
-      <c r="E52" s="97"/>
-      <c r="F52" s="97"/>
+      <c r="E52" s="51"/>
+      <c r="F52" s="51"/>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="26"/>
@@ -2412,56 +2431,42 @@
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
       <c r="D55"/>
-      <c r="E55" s="103"/>
-      <c r="F55" s="104"/>
+      <c r="E55" s="58"/>
+      <c r="F55" s="59"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="25"/>
       <c r="B56"/>
       <c r="C56"/>
       <c r="D56"/>
-      <c r="E56" s="97"/>
-      <c r="F56" s="97"/>
+      <c r="E56" s="51"/>
+      <c r="F56" s="51"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="65">
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="H29:I30"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="J29:K30"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="B29:E30"/>
     <mergeCell ref="F29:G30"/>
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="H44:K44"/>
-    <mergeCell ref="H45:K45"/>
     <mergeCell ref="A34:G34"/>
     <mergeCell ref="H34:I34"/>
     <mergeCell ref="A44:E44"/>
@@ -2473,27 +2478,41 @@
     <mergeCell ref="J35:K35"/>
     <mergeCell ref="H35:I35"/>
     <mergeCell ref="F31:G31"/>
-    <mergeCell ref="H29:I30"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="H45:K45"/>
     <mergeCell ref="F35:G35"/>
-    <mergeCell ref="J29:K30"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="B31:E31"/>
   </mergeCells>
-  <pageMargins left="0.83" right="0.61" top="0.74803149606299213" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="5" firstPageNumber="0" orientation="portrait" horizontalDpi="4294967293" verticalDpi="300" r:id="rId1"/>
+  <pageMargins left="0.78" right="0.11811023622047244" top="0.45" bottom="0.11811023622047244" header="0.73" footer="0.15748031496062992"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="4294967293" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -2501,6 +2520,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
@@ -2516,73 +2538,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" customHeight="1">
-      <c r="A1" s="105" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
+      <c r="A1" s="103" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
     </row>
     <row r="2" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A2" s="105" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
+      <c r="A2" s="103" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
     </row>
     <row r="3" spans="1:9" ht="19.5" customHeight="1">
-      <c r="A3" s="105" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="105"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
+      <c r="A3" s="103" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
     </row>
     <row r="4" spans="1:9" ht="17" customHeight="1"/>
     <row r="5" spans="1:9" s="23" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A5" s="109" t="s">
+      <c r="A5" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="111" t="s">
+      <c r="B5" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="113" t="s">
+      <c r="C5" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="115" t="s">
+      <c r="D5" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="117" t="s">
+      <c r="E5" s="115" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="116"/>
+      <c r="G5" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="118"/>
-      <c r="G5" s="109" t="s">
+      <c r="I5" s="49"/>
+    </row>
+    <row r="6" spans="1:9" s="23" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A6" s="108"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="49"/>
-    </row>
-    <row r="6" spans="1:9" s="23" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A6" s="110"/>
-      <c r="B6" s="112"/>
-      <c r="C6" s="114"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="21" t="s">
-        <v>23</v>
-      </c>
       <c r="F6" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="110"/>
+        <v>58</v>
+      </c>
+      <c r="G6" s="108"/>
       <c r="I6" s="49"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1">
@@ -2590,10 +2612,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="34">
         <v>5250800</v>
@@ -2613,10 +2635,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="34">
         <v>5177500</v>
@@ -2638,10 +2660,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" s="34">
         <v>5427000</v>
@@ -2661,10 +2683,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" s="34">
         <v>5522600</v>
@@ -2684,10 +2706,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="34">
         <v>5061000</v>
@@ -2707,10 +2729,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" s="34">
         <v>4605900</v>
@@ -2730,10 +2752,10 @@
         <v>7</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="34">
         <v>4390900</v>
@@ -2753,10 +2775,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="34">
         <v>4273900</v>
@@ -2778,10 +2800,10 @@
         <v>9</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="34">
         <v>4130300</v>
@@ -2803,10 +2825,10 @@
         <v>10</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" s="34">
         <v>4617100</v>
@@ -2828,10 +2850,10 @@
         <v>11</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="34">
         <v>4021200</v>
@@ -2853,10 +2875,10 @@
         <v>12</v>
       </c>
       <c r="B18" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" s="34">
         <v>3205200</v>
@@ -2876,10 +2898,10 @@
         <v>13</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" s="34">
         <v>3415600</v>
@@ -2901,10 +2923,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="34">
         <v>2651500</v>
@@ -2922,11 +2944,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" s="23" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A21" s="106" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="107"/>
-      <c r="C21" s="108"/>
+      <c r="A21" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="105"/>
+      <c r="C21" s="106"/>
       <c r="D21" s="22">
         <f>SUM(D7:D20)</f>
         <v>61750500</v>
@@ -2977,7 +2999,7 @@
       <c r="D25" s="44"/>
       <c r="E25" s="44"/>
       <c r="F25" s="44" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.5">
@@ -3030,7 +3052,7 @@
     <mergeCell ref="E5:F5"/>
   </mergeCells>
   <pageMargins left="0.41" right="0.12" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="5" scale="90" firstPageNumber="0" orientation="portrait" horizontalDpi="4294967293" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="94" firstPageNumber="0" fitToHeight="0" orientation="portrait" horizontalDpi="4294967293" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>